--- a/llacie/vocabs/micro_antibiotics_TRP.xlsx
+++ b/llacie/vocabs/micro_antibiotics_TRP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trp10/Partners Healthcare Dropbox/Theodore Pak/UCI/src/clarity-snakemake-uci/mapping/uci-ri/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anish/Code/Pak Lab/llacie/llacie/vocabs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A099A742-3BF3-9B48-9D35-3A5875FE552D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63447230-CDB9-8C49-A8CB-AB3D63D605FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3080" yWindow="4080" windowWidth="17160" windowHeight="21000" xr2:uid="{5FF92C89-5F5C-0F4D-9681-072752D9D6F1}"/>
+    <workbookView xWindow="3080" yWindow="760" windowWidth="24660" windowHeight="17080" activeTab="1" xr2:uid="{5FF92C89-5F5C-0F4D-9681-072752D9D6F1}"/>
   </bookViews>
   <sheets>
     <sheet name="antibiotic_map" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1108" uniqueCount="713">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="714">
   <si>
     <t>fosfomycin</t>
   </si>
@@ -2174,6 +2174,9 @@
   </si>
   <si>
     <t>TLT</t>
+  </si>
+  <si>
+    <t>n</t>
   </si>
 </sst>
 </file>
@@ -3088,7 +3091,7 @@
         <v>51</v>
       </c>
       <c r="C2" t="str">
-        <f>_xlfn.XLOOKUP(B2,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B2,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CEF</v>
       </c>
     </row>
@@ -3100,7 +3103,7 @@
         <v>199</v>
       </c>
       <c r="C3" t="str">
-        <f>_xlfn.XLOOKUP(B3,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B3,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>SXT</v>
       </c>
     </row>
@@ -3112,7 +3115,7 @@
         <v>23</v>
       </c>
       <c r="C4" t="str">
-        <f>_xlfn.XLOOKUP(B4,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B4,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>AMK</v>
       </c>
     </row>
@@ -3124,7 +3127,7 @@
         <v>21</v>
       </c>
       <c r="C5" t="str">
-        <f>_xlfn.XLOOKUP(B5,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B5,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>AMC</v>
       </c>
     </row>
@@ -3136,7 +3139,7 @@
         <v>25</v>
       </c>
       <c r="C6" t="str">
-        <f>_xlfn.XLOOKUP(B6,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B6,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>AMP</v>
       </c>
     </row>
@@ -3148,7 +3151,7 @@
         <v>189</v>
       </c>
       <c r="C7" t="str">
-        <f>_xlfn.XLOOKUP(B7,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B7,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>SAM</v>
       </c>
     </row>
@@ -3160,7 +3163,7 @@
         <v>29</v>
       </c>
       <c r="C8" t="str">
-        <f>_xlfn.XLOOKUP(B8,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B8,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>ATM</v>
       </c>
     </row>
@@ -3172,7 +3175,7 @@
         <v>55</v>
       </c>
       <c r="C9" t="str">
-        <f>_xlfn.XLOOKUP(B9,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B9,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CFZ</v>
       </c>
     </row>
@@ -3184,7 +3187,7 @@
         <v>110</v>
       </c>
       <c r="C10" t="str">
-        <f>_xlfn.XLOOKUP(B10,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B10,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>FEP</v>
       </c>
     </row>
@@ -3196,7 +3199,7 @@
         <v>76</v>
       </c>
       <c r="C11" t="str">
-        <f>_xlfn.XLOOKUP(B11,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B11,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CTX</v>
       </c>
     </row>
@@ -3208,7 +3211,7 @@
         <v>115</v>
       </c>
       <c r="C12" t="str">
-        <f>_xlfn.XLOOKUP(B12,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B12,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>FOX</v>
       </c>
     </row>
@@ -3220,7 +3223,7 @@
         <v>43</v>
       </c>
       <c r="C13" t="str">
-        <f>_xlfn.XLOOKUP(B13,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B13,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CAZ</v>
       </c>
     </row>
@@ -3232,7 +3235,7 @@
         <v>80</v>
       </c>
       <c r="C14" t="str">
-        <f>_xlfn.XLOOKUP(B14,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B14,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CXM</v>
       </c>
     </row>
@@ -3244,7 +3247,7 @@
         <v>71</v>
       </c>
       <c r="C15" t="str">
-        <f>_xlfn.XLOOKUP(B15,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B15,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CRO</v>
       </c>
     </row>
@@ -3256,7 +3259,7 @@
         <v>212</v>
       </c>
       <c r="C16" t="str">
-        <f>_xlfn.XLOOKUP(B16,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B16,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>TOB</v>
       </c>
     </row>
@@ -3268,7 +3271,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="str">
-        <f>_xlfn.XLOOKUP(B17,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B17,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CIP</v>
       </c>
     </row>
@@ -3280,7 +3283,7 @@
         <v>103</v>
       </c>
       <c r="C18" t="str">
-        <f>_xlfn.XLOOKUP(B18,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B18,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>ETP</v>
       </c>
     </row>
@@ -3292,7 +3295,7 @@
         <v>5</v>
       </c>
       <c r="C19" t="str">
-        <f>_xlfn.XLOOKUP(B19,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B19,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>GEN</v>
       </c>
     </row>
@@ -3304,7 +3307,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="str">
-        <f>_xlfn.XLOOKUP(B20,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B20,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>IPM</v>
       </c>
     </row>
@@ -3316,7 +3319,7 @@
         <v>2</v>
       </c>
       <c r="C21" t="str">
-        <f>_xlfn.XLOOKUP(B21,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B21,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>LVX</v>
       </c>
     </row>
@@ -3328,7 +3331,7 @@
         <v>143</v>
       </c>
       <c r="C22" t="str">
-        <f>_xlfn.XLOOKUP(B22,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B22,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>MEM</v>
       </c>
     </row>
@@ -3340,7 +3343,7 @@
         <v>160</v>
       </c>
       <c r="C23" t="str">
-        <f>_xlfn.XLOOKUP(B23,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B23,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>NIT</v>
       </c>
     </row>
@@ -3352,7 +3355,7 @@
         <v>8</v>
       </c>
       <c r="C24" t="str">
-        <f>_xlfn.XLOOKUP(B24,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B24,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>PIP</v>
       </c>
     </row>
@@ -3364,7 +3367,7 @@
         <v>220</v>
       </c>
       <c r="C25" t="str">
-        <f>_xlfn.XLOOKUP(B25,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B25,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>TZP</v>
       </c>
     </row>
@@ -3376,7 +3379,7 @@
         <v>201</v>
       </c>
       <c r="C26" t="str">
-        <f>_xlfn.XLOOKUP(B26,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B26,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>TET</v>
       </c>
     </row>
@@ -3388,7 +3391,7 @@
         <v>21</v>
       </c>
       <c r="C27" t="str">
-        <f>_xlfn.XLOOKUP(B27,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B27,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>AMC</v>
       </c>
     </row>
@@ -3400,7 +3403,7 @@
         <v>189</v>
       </c>
       <c r="C28" t="str">
-        <f>_xlfn.XLOOKUP(B28,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B28,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>SAM</v>
       </c>
     </row>
@@ -3412,7 +3415,7 @@
         <v>6</v>
       </c>
       <c r="C29" t="str">
-        <f>_xlfn.XLOOKUP(B29,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B29,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>TGC</v>
       </c>
     </row>
@@ -3424,7 +3427,7 @@
         <v>151</v>
       </c>
       <c r="C30" t="str">
-        <f>_xlfn.XLOOKUP(B30,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B30,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>MIN</v>
       </c>
     </row>
@@ -3436,7 +3439,7 @@
         <v>3</v>
       </c>
       <c r="C31" t="str">
-        <f>_xlfn.XLOOKUP(B31,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B31,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>VAN</v>
       </c>
     </row>
@@ -3448,7 +3451,7 @@
         <v>187</v>
       </c>
       <c r="C32" t="str">
-        <f>_xlfn.XLOOKUP(B32,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B32,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>RIF</v>
       </c>
     </row>
@@ -3460,7 +3463,7 @@
         <v>172</v>
       </c>
       <c r="C33" t="str">
-        <f>_xlfn.XLOOKUP(B33,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B33,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>PEN</v>
       </c>
     </row>
@@ -3472,7 +3475,7 @@
         <v>170</v>
       </c>
       <c r="C34" t="str">
-        <f>_xlfn.XLOOKUP(B34,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B34,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>OXA</v>
       </c>
     </row>
@@ -3484,7 +3487,7 @@
         <v>4</v>
       </c>
       <c r="C35" t="str">
-        <f>_xlfn.XLOOKUP(B35,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B35,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CLI</v>
       </c>
     </row>
@@ -3496,7 +3499,7 @@
         <v>155</v>
       </c>
       <c r="C36" t="str">
-        <f>_xlfn.XLOOKUP(B36,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B36,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>MXF</v>
       </c>
     </row>
@@ -3508,7 +3511,7 @@
         <v>236</v>
       </c>
       <c r="C37" t="str">
-        <f>_xlfn.XLOOKUP(B37,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B37,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>ICR</v>
       </c>
     </row>
@@ -3520,7 +3523,7 @@
         <v>137</v>
       </c>
       <c r="C38" t="str">
-        <f>_xlfn.XLOOKUP(B38,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B38,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>LZD</v>
       </c>
     </row>
@@ -3532,7 +3535,7 @@
         <v>98</v>
       </c>
       <c r="C39" t="str">
-        <f>_xlfn.XLOOKUP(B39,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B39,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>ERY</v>
       </c>
     </row>
@@ -3544,7 +3547,7 @@
         <v>183</v>
       </c>
       <c r="C40" t="str">
-        <f>_xlfn.XLOOKUP(B40,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B40,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>QUD</v>
       </c>
     </row>
@@ -3556,7 +3559,7 @@
         <v>12</v>
       </c>
       <c r="C41" t="str">
-        <f>_xlfn.XLOOKUP(B41,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B41,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>VRC</v>
       </c>
     </row>
@@ -3568,7 +3571,7 @@
         <v>112</v>
       </c>
       <c r="C42" t="str">
-        <f>_xlfn.XLOOKUP(B42,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B42,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>FLC</v>
       </c>
     </row>
@@ -3580,7 +3583,7 @@
         <v>82</v>
       </c>
       <c r="C43" t="str">
-        <f>_xlfn.XLOOKUP(B43,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B43,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>DAP</v>
       </c>
     </row>
@@ -3592,7 +3595,7 @@
         <v>236</v>
       </c>
       <c r="C44" t="str">
-        <f>_xlfn.XLOOKUP(B44,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B44,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>ICR</v>
       </c>
     </row>
@@ -3604,7 +3607,7 @@
         <v>224</v>
       </c>
       <c r="C45" t="str">
-        <f>_xlfn.XLOOKUP(B45,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B45,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>BLAC</v>
       </c>
     </row>
@@ -3616,7 +3619,7 @@
         <v>193</v>
       </c>
       <c r="C46" t="str">
-        <f>_xlfn.XLOOKUP(B46,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B46,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>STR</v>
       </c>
     </row>
@@ -3628,7 +3631,7 @@
         <v>5</v>
       </c>
       <c r="C47" t="str">
-        <f>_xlfn.XLOOKUP(B47,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B47,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>GEN</v>
       </c>
     </row>
@@ -3640,7 +3643,7 @@
         <v>90</v>
       </c>
       <c r="C48" t="str">
-        <f>_xlfn.XLOOKUP(B48,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B48,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>DOX</v>
       </c>
     </row>
@@ -3652,7 +3655,7 @@
         <v>57</v>
       </c>
       <c r="C49" t="str">
-        <f>_xlfn.XLOOKUP(B49,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B49,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CHL</v>
       </c>
     </row>
@@ -3664,7 +3667,7 @@
         <v>170</v>
       </c>
       <c r="C50" t="str">
-        <f>_xlfn.XLOOKUP(B50,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B50,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>OXA</v>
       </c>
     </row>
@@ -3676,7 +3679,7 @@
         <v>0</v>
       </c>
       <c r="C51" t="str">
-        <f>_xlfn.XLOOKUP(B51,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B51,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>FOF</v>
       </c>
     </row>
@@ -3688,7 +3691,7 @@
         <v>0</v>
       </c>
       <c r="C52" t="str">
-        <f>_xlfn.XLOOKUP(B52,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B52,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>FOF</v>
       </c>
     </row>
@@ -3700,7 +3703,7 @@
         <v>170</v>
       </c>
       <c r="C53" t="str">
-        <f>_xlfn.XLOOKUP(B53,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B53,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>OXA</v>
       </c>
     </row>
@@ -3712,7 +3715,7 @@
         <v>183</v>
       </c>
       <c r="C54" t="str">
-        <f>_xlfn.XLOOKUP(B54,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B54,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>QUD</v>
       </c>
     </row>
@@ -3724,7 +3727,7 @@
         <v>189</v>
       </c>
       <c r="C55" t="str">
-        <f>_xlfn.XLOOKUP(B55,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B55,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>SAM</v>
       </c>
     </row>
@@ -3736,7 +3739,7 @@
         <v>55</v>
       </c>
       <c r="C56" t="str">
-        <f>_xlfn.XLOOKUP(B56,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B56,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CFZ</v>
       </c>
     </row>
@@ -3748,7 +3751,7 @@
         <v>41</v>
       </c>
       <c r="C57" t="str">
-        <f>_xlfn.XLOOKUP(B57,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B57,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CAS</v>
       </c>
     </row>
@@ -3760,7 +3763,7 @@
         <v>179</v>
       </c>
       <c r="C58" t="str">
-        <f>_xlfn.XLOOKUP(B58,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B58,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>POS</v>
       </c>
     </row>
@@ -3772,7 +3775,7 @@
         <v>149</v>
       </c>
       <c r="C59" t="str">
-        <f>_xlfn.XLOOKUP(B59,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B59,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>MFG</v>
       </c>
     </row>
@@ -3784,7 +3787,7 @@
         <v>130</v>
       </c>
       <c r="C60" t="str">
-        <f>_xlfn.XLOOKUP(B60,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B60,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>ITC</v>
       </c>
     </row>
@@ -3796,7 +3799,7 @@
         <v>15</v>
       </c>
       <c r="C61" t="str">
-        <f>_xlfn.XLOOKUP(B61,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B61,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>5FC</v>
       </c>
     </row>
@@ -3808,7 +3811,7 @@
         <v>19</v>
       </c>
       <c r="C62" t="str">
-        <f>_xlfn.XLOOKUP(B62,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B62,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>AMB</v>
       </c>
     </row>
@@ -3820,7 +3823,7 @@
         <v>17</v>
       </c>
       <c r="C63" t="str">
-        <f>_xlfn.XLOOKUP(B63,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B63,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>AFG</v>
       </c>
     </row>
@@ -3832,7 +3835,7 @@
         <v>240</v>
       </c>
       <c r="C64" t="str">
-        <f>_xlfn.XLOOKUP(B64,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B64,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>MCIM</v>
       </c>
     </row>
@@ -3844,7 +3847,7 @@
         <v>9</v>
       </c>
       <c r="C65" t="str">
-        <f>_xlfn.XLOOKUP(B65,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B65,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CST</v>
       </c>
     </row>
@@ -3856,7 +3859,7 @@
         <v>5</v>
       </c>
       <c r="C66" t="str">
-        <f>_xlfn.XLOOKUP(B66,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B66,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>GEN</v>
       </c>
     </row>
@@ -3868,7 +3871,7 @@
         <v>1</v>
       </c>
       <c r="C67" t="str">
-        <f>_xlfn.XLOOKUP(B67,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B67,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CIP</v>
       </c>
     </row>
@@ -3880,7 +3883,7 @@
         <v>2</v>
       </c>
       <c r="C68" t="str">
-        <f>_xlfn.XLOOKUP(B68,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B68,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>LVX</v>
       </c>
     </row>
@@ -3892,7 +3895,7 @@
         <v>3</v>
       </c>
       <c r="C69" t="str">
-        <f>_xlfn.XLOOKUP(B69,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B69,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>VAN</v>
       </c>
     </row>
@@ -3904,7 +3907,7 @@
         <v>69</v>
       </c>
       <c r="C70" t="str">
-        <f>_xlfn.XLOOKUP(B70,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B70,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CPT</v>
       </c>
     </row>
@@ -3916,7 +3919,7 @@
         <v>4</v>
       </c>
       <c r="C71" t="str">
-        <f>_xlfn.XLOOKUP(B71,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B71,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CLI</v>
       </c>
     </row>
@@ -3928,7 +3931,7 @@
         <v>5</v>
       </c>
       <c r="C72" t="str">
-        <f>_xlfn.XLOOKUP(B72,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B72,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>GEN</v>
       </c>
     </row>
@@ -3940,7 +3943,7 @@
         <v>199</v>
       </c>
       <c r="C73" t="str">
-        <f>_xlfn.XLOOKUP(B73,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B73,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>SXT</v>
       </c>
     </row>
@@ -3952,7 +3955,7 @@
         <v>6</v>
       </c>
       <c r="C74" t="str">
-        <f>_xlfn.XLOOKUP(B74,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B74,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>TGC</v>
       </c>
     </row>
@@ -3964,7 +3967,7 @@
         <v>96</v>
       </c>
       <c r="C75" t="str">
-        <f>_xlfn.XLOOKUP(B75,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B75,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>ERV</v>
       </c>
     </row>
@@ -3976,7 +3979,7 @@
         <v>147</v>
       </c>
       <c r="C76" t="str">
-        <f>_xlfn.XLOOKUP(B76,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B76,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>MEM_VAB</v>
       </c>
     </row>
@@ -3988,7 +3991,7 @@
         <v>45</v>
       </c>
       <c r="C77" t="str">
-        <f>_xlfn.XLOOKUP(B77,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B77,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CAZ_AVI</v>
       </c>
     </row>
@@ -4000,7 +4003,7 @@
         <v>7</v>
       </c>
       <c r="C78" t="str">
-        <f>_xlfn.XLOOKUP(B78,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B78,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>IPM</v>
       </c>
     </row>
@@ -4012,7 +4015,7 @@
         <v>21</v>
       </c>
       <c r="C79" t="str">
-        <f>_xlfn.XLOOKUP(B79,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B79,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>AMC</v>
       </c>
     </row>
@@ -4024,7 +4027,7 @@
         <v>115</v>
       </c>
       <c r="C80" t="str">
-        <f>_xlfn.XLOOKUP(B80,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B80,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>FOX</v>
       </c>
     </row>
@@ -4036,7 +4039,7 @@
         <v>108</v>
       </c>
       <c r="C81" t="str">
-        <f>_xlfn.XLOOKUP(B81,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B81,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>FDC</v>
       </c>
     </row>
@@ -4048,7 +4051,7 @@
         <v>210</v>
       </c>
       <c r="C82" t="str">
-        <f>_xlfn.XLOOKUP(B82,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B82,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>TMP</v>
       </c>
     </row>
@@ -4060,7 +4063,7 @@
         <v>214</v>
       </c>
       <c r="C83" t="str">
-        <f>_xlfn.XLOOKUP(B83,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B83,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>TOL_TAZ</v>
       </c>
     </row>
@@ -4072,7 +4075,7 @@
         <v>193</v>
       </c>
       <c r="C84" t="str">
-        <f>_xlfn.XLOOKUP(B84,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B84,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>STR</v>
       </c>
     </row>
@@ -4084,7 +4087,7 @@
         <v>5</v>
       </c>
       <c r="C85" t="str">
-        <f>_xlfn.XLOOKUP(B85,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B85,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>GEN</v>
       </c>
     </row>
@@ -4096,7 +4099,7 @@
         <v>63</v>
       </c>
       <c r="C86" t="str">
-        <f>_xlfn.XLOOKUP(B86,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B86,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CLR</v>
       </c>
     </row>
@@ -4108,7 +4111,7 @@
         <v>67</v>
       </c>
       <c r="C87" t="str">
-        <f>_xlfn.XLOOKUP(B87,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B87,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CPD</v>
       </c>
     </row>
@@ -4120,7 +4123,7 @@
         <v>5</v>
       </c>
       <c r="C88" t="str">
-        <f>_xlfn.XLOOKUP(B88,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B88,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>GEN</v>
       </c>
     </row>
@@ -4132,7 +4135,7 @@
         <v>172</v>
       </c>
       <c r="C89" t="str">
-        <f>_xlfn.XLOOKUP(B89,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B89,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>PEN</v>
       </c>
     </row>
@@ -4144,7 +4147,7 @@
         <v>172</v>
       </c>
       <c r="C90" t="str">
-        <f>_xlfn.XLOOKUP(B90,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B90,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>PEN</v>
       </c>
     </row>
@@ -4156,7 +4159,7 @@
         <v>71</v>
       </c>
       <c r="C91" t="str">
-        <f>_xlfn.XLOOKUP(B91,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B91,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CRO</v>
       </c>
     </row>
@@ -4168,7 +4171,7 @@
         <v>71</v>
       </c>
       <c r="C92" t="str">
-        <f>_xlfn.XLOOKUP(B92,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B92,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CRO</v>
       </c>
     </row>
@@ -4180,7 +4183,7 @@
         <v>53</v>
       </c>
       <c r="C93" t="str">
-        <f>_xlfn.XLOOKUP(B93,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B93,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CFM</v>
       </c>
     </row>
@@ -4192,7 +4195,7 @@
         <v>61</v>
       </c>
       <c r="C94" t="str">
-        <f>_xlfn.XLOOKUP(B94,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B94,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CLO</v>
       </c>
     </row>
@@ -4204,7 +4207,7 @@
         <v>193</v>
       </c>
       <c r="C95" t="str">
-        <f>_xlfn.XLOOKUP(B95,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B95,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>STR</v>
       </c>
     </row>
@@ -4216,7 +4219,7 @@
         <v>204</v>
       </c>
       <c r="C96" t="str">
-        <f>_xlfn.XLOOKUP(B96,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B96,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>TIC</v>
       </c>
     </row>
@@ -4228,7 +4231,7 @@
         <v>33</v>
       </c>
       <c r="C97" t="str">
-        <f>_xlfn.XLOOKUP(B97,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B97,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>AZM</v>
       </c>
     </row>
@@ -4240,7 +4243,7 @@
         <v>245</v>
       </c>
       <c r="C98" t="str">
-        <f>_xlfn.XLOOKUP(B98,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B98,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>MEC</v>
       </c>
     </row>
@@ -4252,7 +4255,7 @@
         <v>244</v>
       </c>
       <c r="C99" t="str">
-        <f>_xlfn.XLOOKUP(B99,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B99,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>ESBL</v>
       </c>
     </row>
@@ -4264,7 +4267,7 @@
         <v>8</v>
       </c>
       <c r="C100" t="str">
-        <f>_xlfn.XLOOKUP(B100,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B100,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>PIP</v>
       </c>
     </row>
@@ -4276,7 +4279,7 @@
         <v>197</v>
       </c>
       <c r="C101" t="str">
-        <f>_xlfn.XLOOKUP(B101,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B101,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>SXM</v>
       </c>
     </row>
@@ -4288,7 +4291,7 @@
         <v>74</v>
       </c>
       <c r="C102" t="str">
-        <f>_xlfn.XLOOKUP(B102,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B102,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CTT</v>
       </c>
     </row>
@@ -4300,7 +4303,7 @@
         <v>9</v>
       </c>
       <c r="C103" t="str">
-        <f>_xlfn.XLOOKUP(B103,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B103,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CST</v>
       </c>
     </row>
@@ -4312,7 +4315,7 @@
         <v>128</v>
       </c>
       <c r="C104" t="str">
-        <f>_xlfn.XLOOKUP(B104,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B104,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>ISA</v>
       </c>
     </row>
@@ -4324,7 +4327,7 @@
         <v>243</v>
       </c>
       <c r="C105" t="str">
-        <f>_xlfn.XLOOKUP(B105,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B105,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CARBA</v>
       </c>
     </row>
@@ -4336,7 +4339,7 @@
         <v>172</v>
       </c>
       <c r="C106" t="str">
-        <f>_xlfn.XLOOKUP(B106,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B106,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>PEN</v>
       </c>
     </row>
@@ -4348,7 +4351,7 @@
         <v>170</v>
       </c>
       <c r="C107" t="str">
-        <f>_xlfn.XLOOKUP(B107,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B107,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>OXA</v>
       </c>
     </row>
@@ -4360,7 +4363,7 @@
         <v>172</v>
       </c>
       <c r="C108" t="str">
-        <f>_xlfn.XLOOKUP(B108,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B108,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>PEN</v>
       </c>
     </row>
@@ -4372,7 +4375,7 @@
         <v>126</v>
       </c>
       <c r="C109" t="str">
-        <f>_xlfn.XLOOKUP(B109,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B109,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>IPM_REL</v>
       </c>
     </row>
@@ -4384,7 +4387,7 @@
         <v>236</v>
       </c>
       <c r="C110" t="str">
-        <f>_xlfn.XLOOKUP(B110,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B110,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>ICR</v>
       </c>
     </row>
@@ -4396,7 +4399,7 @@
         <v>172</v>
       </c>
       <c r="C111" t="str">
-        <f>_xlfn.XLOOKUP(B111,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B111,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>PEN</v>
       </c>
     </row>
@@ -4408,7 +4411,7 @@
         <v>181</v>
       </c>
       <c r="C112" t="str">
-        <f>_xlfn.XLOOKUP(B112,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B112,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>PZA</v>
       </c>
     </row>
@@ -4420,7 +4423,7 @@
         <v>92</v>
       </c>
       <c r="C113" t="str">
-        <f>_xlfn.XLOOKUP(B113,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B113,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>EMB</v>
       </c>
     </row>
@@ -4432,7 +4435,7 @@
         <v>123</v>
       </c>
       <c r="C114" t="str">
-        <f>_xlfn.XLOOKUP(B114,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B114,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>INH</v>
       </c>
     </row>
@@ -4444,7 +4447,7 @@
         <v>123</v>
       </c>
       <c r="C115" t="str">
-        <f>_xlfn.XLOOKUP(B115,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B115,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>INH</v>
       </c>
     </row>
@@ -4456,7 +4459,7 @@
         <v>84</v>
       </c>
       <c r="C116" t="str">
-        <f>_xlfn.XLOOKUP(B116,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B116,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>DCS</v>
       </c>
     </row>
@@ -4468,7 +4471,7 @@
         <v>92</v>
       </c>
       <c r="C117" t="str">
-        <f>_xlfn.XLOOKUP(B117,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B117,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>EMB</v>
       </c>
     </row>
@@ -4480,7 +4483,7 @@
         <v>23</v>
       </c>
       <c r="C118" t="str">
-        <f>_xlfn.XLOOKUP(B118,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B118,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>AMK</v>
       </c>
     </row>
@@ -4492,7 +4495,7 @@
         <v>193</v>
       </c>
       <c r="C119" t="str">
-        <f>_xlfn.XLOOKUP(B119,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B119,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>STR</v>
       </c>
     </row>
@@ -4504,7 +4507,7 @@
         <v>187</v>
       </c>
       <c r="C120" t="str">
-        <f>_xlfn.XLOOKUP(B120,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B120,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>RIF</v>
       </c>
     </row>
@@ -4516,7 +4519,7 @@
         <v>123</v>
       </c>
       <c r="C121" t="str">
-        <f>_xlfn.XLOOKUP(B121,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B121,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>INH</v>
       </c>
     </row>
@@ -4528,7 +4531,7 @@
         <v>155</v>
       </c>
       <c r="C122" t="str">
-        <f>_xlfn.XLOOKUP(B122,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B122,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>MXF</v>
       </c>
     </row>
@@ -4540,7 +4543,7 @@
         <v>101</v>
       </c>
       <c r="C123" t="str">
-        <f>_xlfn.XLOOKUP(B123,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B123,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>ETO</v>
       </c>
     </row>
@@ -4552,7 +4555,7 @@
         <v>132</v>
       </c>
       <c r="C124" t="str">
-        <f>_xlfn.XLOOKUP(B124,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B124,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>KAN</v>
       </c>
     </row>
@@ -4564,7 +4567,7 @@
         <v>38</v>
       </c>
       <c r="C125" t="str">
-        <f>_xlfn.XLOOKUP(B125,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B125,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CAP</v>
       </c>
     </row>
@@ -4576,7 +4579,7 @@
         <v>123</v>
       </c>
       <c r="C126" t="str">
-        <f>_xlfn.XLOOKUP(B126,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B126,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>INH</v>
       </c>
     </row>
@@ -4588,7 +4591,7 @@
         <v>242</v>
       </c>
       <c r="C127" t="str">
-        <f>_xlfn.XLOOKUP(B127,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B127,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CARBA</v>
       </c>
     </row>
@@ -4600,7 +4603,7 @@
         <v>246</v>
       </c>
       <c r="C128" t="str">
-        <f>_xlfn.XLOOKUP(B128,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B128,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CARBA</v>
       </c>
     </row>
@@ -4612,7 +4615,7 @@
         <v>241</v>
       </c>
       <c r="C129" t="str">
-        <f>_xlfn.XLOOKUP(B129,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B129,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CARBA</v>
       </c>
     </row>
@@ -4624,7 +4627,7 @@
         <v>247</v>
       </c>
       <c r="C130" t="str">
-        <f>_xlfn.XLOOKUP(B130,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B130,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CARBA</v>
       </c>
     </row>
@@ -4636,7 +4639,7 @@
         <v>239</v>
       </c>
       <c r="C131" t="str">
-        <f>_xlfn.XLOOKUP(B131,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B131,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CARBA</v>
       </c>
     </row>
@@ -4648,7 +4651,7 @@
         <v>216</v>
       </c>
       <c r="C132" t="str">
-        <f>_xlfn.XLOOKUP(B132,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B132,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>TRB</v>
       </c>
     </row>
@@ -4660,7 +4663,7 @@
         <v>185</v>
       </c>
       <c r="C133" t="str">
-        <f>_xlfn.XLOOKUP(B133,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B133,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>RFB</v>
       </c>
     </row>
@@ -4672,7 +4675,7 @@
         <v>199</v>
       </c>
       <c r="C134" t="str">
-        <f>_xlfn.XLOOKUP(B134,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B134,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>SXT</v>
       </c>
     </row>
@@ -4684,7 +4687,7 @@
         <v>166</v>
       </c>
       <c r="C135" t="str">
-        <f>_xlfn.XLOOKUP(B135,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B135,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>OFX</v>
       </c>
     </row>
@@ -4696,7 +4699,7 @@
         <v>183</v>
       </c>
       <c r="C136" t="str">
-        <f>_xlfn.XLOOKUP(B136,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B136,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>QUD</v>
       </c>
     </row>
@@ -4708,7 +4711,7 @@
         <v>15</v>
       </c>
       <c r="C137" t="str">
-        <f>_xlfn.XLOOKUP(B137,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B137,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>5FC</v>
       </c>
     </row>
@@ -4720,7 +4723,7 @@
         <v>12</v>
       </c>
       <c r="C138" t="str">
-        <f>_xlfn.XLOOKUP(B138,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B138,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>VRC</v>
       </c>
     </row>
@@ -4732,7 +4735,7 @@
         <v>193</v>
       </c>
       <c r="C139" t="str">
-        <f>_xlfn.XLOOKUP(B139,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B139,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>STR</v>
       </c>
     </row>
@@ -4744,7 +4747,7 @@
         <v>49</v>
       </c>
       <c r="C140" t="str">
-        <f>_xlfn.XLOOKUP(B140,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B140,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CEC</v>
       </c>
     </row>
@@ -4756,7 +4759,7 @@
         <v>191</v>
       </c>
       <c r="C141" t="str">
-        <f>_xlfn.XLOOKUP(B141,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B141,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>SPT</v>
       </c>
     </row>
@@ -4768,7 +4771,7 @@
         <v>243</v>
       </c>
       <c r="C142" t="str">
-        <f>_xlfn.XLOOKUP(B142,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B142,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CARBA</v>
       </c>
     </row>
@@ -4780,7 +4783,7 @@
         <v>193</v>
       </c>
       <c r="C143" t="str">
-        <f>_xlfn.XLOOKUP(B143,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B143,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>STR</v>
       </c>
     </row>
@@ -4792,7 +4795,7 @@
         <v>94</v>
       </c>
       <c r="C144" t="str">
-        <f>_xlfn.XLOOKUP(B144,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B144,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>EMB_RIF</v>
       </c>
     </row>
@@ -4804,7 +4807,7 @@
         <v>187</v>
       </c>
       <c r="C145" t="str">
-        <f>_xlfn.XLOOKUP(B145,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B145,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>RIF</v>
       </c>
     </row>
@@ -4816,7 +4819,7 @@
         <v>92</v>
       </c>
       <c r="C146" t="str">
-        <f>_xlfn.XLOOKUP(B146,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B146,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>EMB</v>
       </c>
     </row>
@@ -4828,7 +4831,7 @@
         <v>208</v>
       </c>
       <c r="C147" t="str">
-        <f>_xlfn.XLOOKUP(B147,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B147,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>TLV</v>
       </c>
     </row>
@@ -4840,7 +4843,7 @@
         <v>27</v>
       </c>
       <c r="C148" t="str">
-        <f>_xlfn.XLOOKUP(B148,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B148,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>AMX</v>
       </c>
     </row>
@@ -4852,7 +4855,7 @@
         <v>248</v>
       </c>
       <c r="C149" t="str">
-        <f>_xlfn.XLOOKUP(B149,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B149,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>RZF</v>
       </c>
     </row>
@@ -4864,7 +4867,7 @@
         <v>153</v>
       </c>
       <c r="C150" t="str">
-        <f>_xlfn.XLOOKUP(B150,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B150,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>MTZ</v>
       </c>
     </row>
@@ -4876,7 +4879,7 @@
         <v>224</v>
       </c>
       <c r="C151" t="str">
-        <f>_xlfn.XLOOKUP(B151,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B151,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>BLAC</v>
       </c>
     </row>
@@ -4888,7 +4891,7 @@
         <v>88</v>
       </c>
       <c r="C152" t="str">
-        <f>_xlfn.XLOOKUP(B152,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B152,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>DOR</v>
       </c>
     </row>
@@ -4900,7 +4903,7 @@
         <v>175</v>
       </c>
       <c r="C153" t="str">
-        <f>_xlfn.XLOOKUP(B153,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B153,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>PLZ</v>
       </c>
     </row>
@@ -4912,7 +4915,7 @@
         <v>170</v>
       </c>
       <c r="C154" t="str">
-        <f>_xlfn.XLOOKUP(B154,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B154,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>OXA</v>
       </c>
     </row>
@@ -4924,7 +4927,7 @@
         <v>168</v>
       </c>
       <c r="C155" t="str">
-        <f>_xlfn.XLOOKUP(B155,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B155,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>OMC</v>
       </c>
     </row>
@@ -4936,7 +4939,7 @@
         <v>86</v>
       </c>
       <c r="C156" t="str">
-        <f>_xlfn.XLOOKUP(B156,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B156,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>DLX</v>
       </c>
     </row>
@@ -4948,7 +4951,7 @@
         <v>195</v>
       </c>
       <c r="C157" t="str">
-        <f>_xlfn.XLOOKUP(B157,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B157,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>SUL_DUR</v>
       </c>
     </row>
@@ -4960,7 +4963,7 @@
         <v>31</v>
       </c>
       <c r="C158" t="str">
-        <f>_xlfn.XLOOKUP(B158,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B158,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>ATM_AVI</v>
       </c>
     </row>
@@ -4972,7 +4975,7 @@
         <v>47</v>
       </c>
       <c r="C159" t="str">
-        <f>_xlfn.XLOOKUP(B159,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B159,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CAZ_CLV</v>
       </c>
     </row>
@@ -4984,7 +4987,7 @@
         <v>78</v>
       </c>
       <c r="C160" t="str">
-        <f>_xlfn.XLOOKUP(B160,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B160,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CTX_CLV</v>
       </c>
     </row>
@@ -4996,7 +4999,7 @@
         <v>199</v>
       </c>
       <c r="C161" t="str">
-        <f>_xlfn.XLOOKUP(B161,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B161,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>SXT</v>
       </c>
     </row>
@@ -5008,7 +5011,7 @@
         <v>140</v>
       </c>
       <c r="C162" t="str">
-        <f>_xlfn.XLOOKUP(B162,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B162,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>MCZ</v>
       </c>
     </row>
@@ -5020,7 +5023,7 @@
         <v>218</v>
       </c>
       <c r="C163" t="str">
-        <f>_xlfn.XLOOKUP(B163,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B163,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>TRC</v>
       </c>
     </row>
@@ -5032,7 +5035,7 @@
         <v>35</v>
       </c>
       <c r="C164" t="str">
-        <f>_xlfn.XLOOKUP(B164,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B164,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>BDQ</v>
       </c>
     </row>
@@ -5044,7 +5047,7 @@
         <v>172</v>
       </c>
       <c r="C165" t="str">
-        <f>_xlfn.XLOOKUP(B165,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B165,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>PEN</v>
       </c>
     </row>
@@ -5056,7 +5059,7 @@
         <v>172</v>
       </c>
       <c r="C166" t="str">
-        <f>_xlfn.XLOOKUP(B166,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B166,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>PEN</v>
       </c>
     </row>
@@ -5068,7 +5071,7 @@
         <v>71</v>
       </c>
       <c r="C167" t="str">
-        <f>_xlfn.XLOOKUP(B167,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B167,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CRO</v>
       </c>
     </row>
@@ -5080,7 +5083,7 @@
         <v>76</v>
       </c>
       <c r="C168" t="str">
-        <f>_xlfn.XLOOKUP(B168,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B168,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CTX</v>
       </c>
     </row>
@@ -5092,7 +5095,7 @@
         <v>76</v>
       </c>
       <c r="C169" t="str">
-        <f>_xlfn.XLOOKUP(B169,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B169,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CTX</v>
       </c>
     </row>
@@ -5104,7 +5107,7 @@
         <v>187</v>
       </c>
       <c r="C170" t="str">
-        <f>_xlfn.XLOOKUP(B170,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B170,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>RIF</v>
       </c>
     </row>
@@ -5116,7 +5119,7 @@
         <v>181</v>
       </c>
       <c r="C171" t="str">
-        <f>_xlfn.XLOOKUP(B171,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B171,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>PZA</v>
       </c>
     </row>
@@ -5128,7 +5131,7 @@
         <v>172</v>
       </c>
       <c r="C172" t="str">
-        <f>_xlfn.XLOOKUP(B172,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B172,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>PEN</v>
       </c>
     </row>
@@ -5140,7 +5143,7 @@
         <v>71</v>
       </c>
       <c r="C173" t="str">
-        <f>_xlfn.XLOOKUP(B173,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B173,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CRO</v>
       </c>
     </row>
@@ -5152,7 +5155,7 @@
         <v>71</v>
       </c>
       <c r="C174" t="str">
-        <f>_xlfn.XLOOKUP(B174,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B174,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CRO</v>
       </c>
     </row>
@@ -5164,7 +5167,7 @@
         <v>134</v>
       </c>
       <c r="C175" t="str">
-        <f>_xlfn.XLOOKUP(B175,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B175,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>KTC</v>
       </c>
     </row>
@@ -5176,7 +5179,7 @@
         <v>92</v>
       </c>
       <c r="C176" t="str">
-        <f>_xlfn.XLOOKUP(B176,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B176,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>EMB</v>
       </c>
     </row>
@@ -5188,7 +5191,7 @@
         <v>123</v>
       </c>
       <c r="C177" t="str">
-        <f>_xlfn.XLOOKUP(B177,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B177,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>INH</v>
       </c>
     </row>
@@ -5200,7 +5203,7 @@
         <v>193</v>
       </c>
       <c r="C178" t="str">
-        <f>_xlfn.XLOOKUP(B178,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B178,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>STR</v>
       </c>
     </row>
@@ -5212,7 +5215,7 @@
         <v>177</v>
       </c>
       <c r="C179" t="str">
-        <f>_xlfn.XLOOKUP(B179,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B179,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>PMB</v>
       </c>
     </row>
@@ -5224,7 +5227,7 @@
         <v>71</v>
       </c>
       <c r="C180" t="str">
-        <f>_xlfn.XLOOKUP(B180,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B180,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CRO</v>
       </c>
     </row>
@@ -5236,7 +5239,7 @@
         <v>145</v>
       </c>
       <c r="C181" t="str">
-        <f>_xlfn.XLOOKUP(B181,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B181,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>MEM_IMI</v>
       </c>
     </row>
@@ -5248,7 +5251,7 @@
         <v>132</v>
       </c>
       <c r="C182" t="str">
-        <f>_xlfn.XLOOKUP(B182,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B182,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>KAN</v>
       </c>
     </row>
@@ -5260,7 +5263,7 @@
         <v>164</v>
       </c>
       <c r="C183" t="str">
-        <f>_xlfn.XLOOKUP(B183,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B183,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>NYT</v>
       </c>
     </row>
@@ -5272,7 +5275,7 @@
         <v>120</v>
       </c>
       <c r="C184" t="str">
-        <f>_xlfn.XLOOKUP(B184,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B184,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>GRF</v>
       </c>
     </row>
@@ -5284,7 +5287,7 @@
         <v>76</v>
       </c>
       <c r="C185" t="str">
-        <f>_xlfn.XLOOKUP(B185,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B185,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CTX</v>
       </c>
     </row>
@@ -5296,7 +5299,7 @@
         <v>158</v>
       </c>
       <c r="C186" t="str">
-        <f>_xlfn.XLOOKUP(B186,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B186,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>NAT</v>
       </c>
     </row>
@@ -5308,7 +5311,7 @@
         <v>65</v>
       </c>
       <c r="C187" t="str">
-        <f>_xlfn.XLOOKUP(B187,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B187,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CLT</v>
       </c>
     </row>
@@ -5320,7 +5323,7 @@
         <v>236</v>
       </c>
       <c r="C188" t="str">
-        <f>_xlfn.XLOOKUP(B188,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B188,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>ICR</v>
       </c>
     </row>
@@ -5332,7 +5335,7 @@
         <v>250</v>
       </c>
       <c r="C189" t="str">
-        <f>_xlfn.XLOOKUP(B189,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B189,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>NAL</v>
       </c>
     </row>
@@ -5344,7 +5347,7 @@
         <v>249</v>
       </c>
       <c r="C190" t="str">
-        <f>_xlfn.XLOOKUP(B190,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B190,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CZX</v>
       </c>
     </row>
@@ -5356,7 +5359,7 @@
         <v>214</v>
       </c>
       <c r="C191" t="str">
-        <f>_xlfn.XLOOKUP(B191,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B191,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>TOL_TAZ</v>
       </c>
     </row>
@@ -5368,7 +5371,7 @@
         <v>597</v>
       </c>
       <c r="C192" t="str">
-        <f>_xlfn.XLOOKUP(B192,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B192,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CFP</v>
       </c>
     </row>
@@ -5380,7 +5383,7 @@
         <v>76</v>
       </c>
       <c r="C193" t="str">
-        <f>_xlfn.XLOOKUP(B193,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B193,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CTX</v>
       </c>
     </row>
@@ -5392,7 +5395,7 @@
         <v>71</v>
       </c>
       <c r="C194" t="str">
-        <f>_xlfn.XLOOKUP(B194,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B194,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CRO</v>
       </c>
     </row>
@@ -5404,7 +5407,7 @@
         <v>251</v>
       </c>
       <c r="C195" t="str">
-        <f>_xlfn.XLOOKUP(B195,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B195,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>FA</v>
       </c>
     </row>
@@ -5416,7 +5419,7 @@
         <v>193</v>
       </c>
       <c r="C196" t="str">
-        <f>_xlfn.XLOOKUP(B196,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B196,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>STR</v>
       </c>
     </row>
@@ -5428,7 +5431,7 @@
         <v>15</v>
       </c>
       <c r="C197" t="str">
-        <f>_xlfn.XLOOKUP(B197,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B197,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>5FC</v>
       </c>
     </row>
@@ -5440,7 +5443,7 @@
         <v>23</v>
       </c>
       <c r="C198" t="str">
-        <f>_xlfn.XLOOKUP(B198,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B198,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>AMK</v>
       </c>
     </row>
@@ -5452,7 +5455,7 @@
         <v>23</v>
       </c>
       <c r="C199" t="str">
-        <f>_xlfn.XLOOKUP(B199,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B199,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>AMK</v>
       </c>
     </row>
@@ -5464,7 +5467,7 @@
         <v>19</v>
       </c>
       <c r="C200" t="str">
-        <f>_xlfn.XLOOKUP(B200,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B200,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>AMB</v>
       </c>
     </row>
@@ -5476,7 +5479,7 @@
         <v>21</v>
       </c>
       <c r="C201" t="str">
-        <f>_xlfn.XLOOKUP(B201,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B201,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>AMC</v>
       </c>
     </row>
@@ -5488,7 +5491,7 @@
         <v>546</v>
       </c>
       <c r="C202" t="str">
-        <f>_xlfn.XLOOKUP(B202,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B202,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>AZL</v>
       </c>
     </row>
@@ -5500,7 +5503,7 @@
         <v>548</v>
       </c>
       <c r="C203" t="str">
-        <f>_xlfn.XLOOKUP(B203,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B203,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>BAC</v>
       </c>
     </row>
@@ -5512,7 +5515,7 @@
         <v>224</v>
       </c>
       <c r="C204" t="str">
-        <f>_xlfn.XLOOKUP(B204,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B204,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>BLAC</v>
       </c>
     </row>
@@ -5524,7 +5527,7 @@
         <v>224</v>
       </c>
       <c r="C205" t="str">
-        <f>_xlfn.XLOOKUP(B205,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B205,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>BLAC</v>
       </c>
     </row>
@@ -5536,7 +5539,7 @@
         <v>38</v>
       </c>
       <c r="C206" t="str">
-        <f>_xlfn.XLOOKUP(B206,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B206,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CAP</v>
       </c>
     </row>
@@ -5548,7 +5551,7 @@
         <v>38</v>
       </c>
       <c r="C207" t="str">
-        <f>_xlfn.XLOOKUP(B207,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B207,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CAP</v>
       </c>
     </row>
@@ -5560,7 +5563,7 @@
         <v>38</v>
       </c>
       <c r="C208" t="str">
-        <f>_xlfn.XLOOKUP(B208,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B208,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CAP</v>
       </c>
     </row>
@@ -5572,7 +5575,7 @@
         <v>243</v>
       </c>
       <c r="C209" t="str">
-        <f>_xlfn.XLOOKUP(B209,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B209,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CARBA</v>
       </c>
     </row>
@@ -5584,7 +5587,7 @@
         <v>550</v>
       </c>
       <c r="C210" t="str">
-        <f>_xlfn.XLOOKUP(B210,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B210,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CRB</v>
       </c>
     </row>
@@ -5596,7 +5599,7 @@
         <v>106</v>
       </c>
       <c r="C211" t="str">
-        <f>_xlfn.XLOOKUP(B211,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B211,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>FAM</v>
       </c>
     </row>
@@ -5608,7 +5611,7 @@
         <v>55</v>
       </c>
       <c r="C212" t="str">
-        <f>_xlfn.XLOOKUP(B212,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B212,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CFZ</v>
       </c>
     </row>
@@ -5620,7 +5623,7 @@
         <v>55</v>
       </c>
       <c r="C213" t="str">
-        <f>_xlfn.XLOOKUP(B213,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B213,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CFZ</v>
       </c>
     </row>
@@ -5632,7 +5635,7 @@
         <v>55</v>
       </c>
       <c r="C214" t="str">
-        <f>_xlfn.XLOOKUP(B214,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B214,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CFZ</v>
       </c>
     </row>
@@ -5644,7 +5647,7 @@
         <v>110</v>
       </c>
       <c r="C215" t="str">
-        <f>_xlfn.XLOOKUP(B215,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B215,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>FEP</v>
       </c>
     </row>
@@ -5656,7 +5659,7 @@
         <v>552</v>
       </c>
       <c r="C216" t="str">
-        <f>_xlfn.XLOOKUP(B216,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B216,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CID</v>
       </c>
     </row>
@@ -5668,7 +5671,7 @@
         <v>554</v>
       </c>
       <c r="C217" t="str">
-        <f>_xlfn.XLOOKUP(B217,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B217,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CND</v>
       </c>
     </row>
@@ -5680,7 +5683,7 @@
         <v>76</v>
       </c>
       <c r="C218" t="str">
-        <f>_xlfn.XLOOKUP(B218,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B218,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CTX</v>
       </c>
     </row>
@@ -5692,7 +5695,7 @@
         <v>76</v>
       </c>
       <c r="C219" t="str">
-        <f>_xlfn.XLOOKUP(B219,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B219,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CTX</v>
       </c>
     </row>
@@ -5704,7 +5707,7 @@
         <v>78</v>
       </c>
       <c r="C220" t="str">
-        <f>_xlfn.XLOOKUP(B220,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B220,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CTX_CLV</v>
       </c>
     </row>
@@ -5716,7 +5719,7 @@
         <v>556</v>
       </c>
       <c r="C221" t="str">
-        <f>_xlfn.XLOOKUP(B221,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B221,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CTF</v>
       </c>
     </row>
@@ -5728,7 +5731,7 @@
         <v>67</v>
       </c>
       <c r="C222" t="str">
-        <f>_xlfn.XLOOKUP(B222,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B222,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CPD</v>
       </c>
     </row>
@@ -5740,7 +5743,7 @@
         <v>45</v>
       </c>
       <c r="C223" t="str">
-        <f>_xlfn.XLOOKUP(B223,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B223,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CAZ_AVI</v>
       </c>
     </row>
@@ -5752,7 +5755,7 @@
         <v>47</v>
       </c>
       <c r="C224" t="str">
-        <f>_xlfn.XLOOKUP(B224,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B224,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CAZ_CLV</v>
       </c>
     </row>
@@ -5764,7 +5767,7 @@
         <v>71</v>
       </c>
       <c r="C225" t="str">
-        <f>_xlfn.XLOOKUP(B225,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B225,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CRO</v>
       </c>
     </row>
@@ -5776,7 +5779,7 @@
         <v>71</v>
       </c>
       <c r="C226" t="str">
-        <f>_xlfn.XLOOKUP(B226,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B226,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CRO</v>
       </c>
     </row>
@@ -5788,7 +5791,7 @@
         <v>80</v>
       </c>
       <c r="C227" t="str">
-        <f>_xlfn.XLOOKUP(B227,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B227,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CXM</v>
       </c>
     </row>
@@ -5800,7 +5803,7 @@
         <v>80</v>
       </c>
       <c r="C228" t="str">
-        <f>_xlfn.XLOOKUP(B228,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B228,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CXM</v>
       </c>
     </row>
@@ -5812,7 +5815,7 @@
         <v>558</v>
       </c>
       <c r="C229" t="str">
-        <f>_xlfn.XLOOKUP(B229,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B229,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>LEX</v>
       </c>
     </row>
@@ -5824,7 +5827,7 @@
         <v>560</v>
       </c>
       <c r="C230" t="str">
-        <f>_xlfn.XLOOKUP(B230,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B230,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CED</v>
       </c>
     </row>
@@ -5836,7 +5839,7 @@
         <v>1</v>
       </c>
       <c r="C231" t="str">
-        <f>_xlfn.XLOOKUP(B231,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B231,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CIP</v>
       </c>
     </row>
@@ -5848,7 +5851,7 @@
         <v>63</v>
       </c>
       <c r="C232" t="str">
-        <f>_xlfn.XLOOKUP(B232,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B232,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CLR</v>
       </c>
     </row>
@@ -5860,7 +5863,7 @@
         <v>63</v>
       </c>
       <c r="C233" t="str">
-        <f>_xlfn.XLOOKUP(B233,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B233,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CLR</v>
       </c>
     </row>
@@ -5872,7 +5875,7 @@
         <v>63</v>
       </c>
       <c r="C234" t="str">
-        <f>_xlfn.XLOOKUP(B234,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B234,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CLR</v>
       </c>
     </row>
@@ -5884,7 +5887,7 @@
         <v>562</v>
       </c>
       <c r="C235" t="str">
-        <f>_xlfn.XLOOKUP(B235,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B235,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CLX</v>
       </c>
     </row>
@@ -5896,7 +5899,7 @@
         <v>61</v>
       </c>
       <c r="C236" t="str">
-        <f>_xlfn.XLOOKUP(B236,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B236,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CLO</v>
       </c>
     </row>
@@ -5908,7 +5911,7 @@
         <v>61</v>
       </c>
       <c r="C237" t="str">
-        <f>_xlfn.XLOOKUP(B237,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B237,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CLO</v>
       </c>
     </row>
@@ -5920,7 +5923,7 @@
         <v>243</v>
       </c>
       <c r="C238" t="str">
-        <f>_xlfn.XLOOKUP(B238,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B238,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CARBA</v>
       </c>
     </row>
@@ -5932,7 +5935,7 @@
         <v>84</v>
       </c>
       <c r="C239" t="str">
-        <f>_xlfn.XLOOKUP(B239,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B239,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>DCS</v>
       </c>
     </row>
@@ -5944,7 +5947,7 @@
         <v>84</v>
       </c>
       <c r="C240" t="str">
-        <f>_xlfn.XLOOKUP(B240,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B240,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>DCS</v>
       </c>
     </row>
@@ -5956,7 +5959,7 @@
         <v>4</v>
       </c>
       <c r="C241" t="str">
-        <f>_xlfn.XLOOKUP(B241,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B241,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CLI</v>
       </c>
     </row>
@@ -5968,7 +5971,7 @@
         <v>545</v>
       </c>
       <c r="C242" t="str">
-        <f>_xlfn.XLOOKUP(B242,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B242,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>DAL</v>
       </c>
     </row>
@@ -5980,7 +5983,7 @@
         <v>565</v>
       </c>
       <c r="C243" t="str">
-        <f>_xlfn.XLOOKUP(B243,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B243,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>DIC</v>
       </c>
     </row>
@@ -5992,7 +5995,7 @@
         <v>244</v>
       </c>
       <c r="C244" t="str">
-        <f>_xlfn.XLOOKUP(B244,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B244,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>ESBL</v>
       </c>
     </row>
@@ -6004,7 +6007,7 @@
         <v>244</v>
       </c>
       <c r="C245" t="str">
-        <f>_xlfn.XLOOKUP(B245,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B245,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>ESBL</v>
       </c>
     </row>
@@ -6016,7 +6019,7 @@
         <v>94</v>
       </c>
       <c r="C246" t="str">
-        <f>_xlfn.XLOOKUP(B246,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B246,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>EMB_RIF</v>
       </c>
     </row>
@@ -6028,7 +6031,7 @@
         <v>92</v>
       </c>
       <c r="C247" t="str">
-        <f>_xlfn.XLOOKUP(B247,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B247,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>EMB</v>
       </c>
     </row>
@@ -6040,7 +6043,7 @@
         <v>92</v>
       </c>
       <c r="C248" t="str">
-        <f>_xlfn.XLOOKUP(B248,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B248,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>EMB</v>
       </c>
     </row>
@@ -6052,7 +6055,7 @@
         <v>92</v>
       </c>
       <c r="C249" t="str">
-        <f>_xlfn.XLOOKUP(B249,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B249,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>EMB</v>
       </c>
     </row>
@@ -6064,7 +6067,7 @@
         <v>101</v>
       </c>
       <c r="C250" t="str">
-        <f>_xlfn.XLOOKUP(B250,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B250,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>ETO</v>
       </c>
     </row>
@@ -6076,7 +6079,7 @@
         <v>101</v>
       </c>
       <c r="C251" t="str">
-        <f>_xlfn.XLOOKUP(B251,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B251,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>ETO</v>
       </c>
     </row>
@@ -6088,7 +6091,7 @@
         <v>101</v>
       </c>
       <c r="C252" t="str">
-        <f>_xlfn.XLOOKUP(B252,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B252,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>ETO</v>
       </c>
     </row>
@@ -6100,7 +6103,7 @@
         <v>112</v>
       </c>
       <c r="C253" t="str">
-        <f>_xlfn.XLOOKUP(B253,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B253,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>FLC</v>
       </c>
     </row>
@@ -6112,7 +6115,7 @@
         <v>117</v>
       </c>
       <c r="C254" t="str">
-        <f>_xlfn.XLOOKUP(B254,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B254,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>GAT</v>
       </c>
     </row>
@@ -6124,7 +6127,7 @@
         <v>5</v>
       </c>
       <c r="C255" t="str">
-        <f>_xlfn.XLOOKUP(B255,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B255,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>GEN</v>
       </c>
     </row>
@@ -6136,7 +6139,7 @@
         <v>5</v>
       </c>
       <c r="C256" t="str">
-        <f>_xlfn.XLOOKUP(B256,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B256,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>GEN</v>
       </c>
     </row>
@@ -6148,7 +6151,7 @@
         <v>5</v>
       </c>
       <c r="C257" t="str">
-        <f>_xlfn.XLOOKUP(B257,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B257,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>GEN</v>
       </c>
     </row>
@@ -6160,7 +6163,7 @@
         <v>126</v>
       </c>
       <c r="C258" t="str">
-        <f>_xlfn.XLOOKUP(B258,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B258,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>IPM_REL</v>
       </c>
     </row>
@@ -6172,7 +6175,7 @@
         <v>241</v>
       </c>
       <c r="C259" t="str">
-        <f>_xlfn.XLOOKUP(B259,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B259,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CARBA</v>
       </c>
     </row>
@@ -6184,7 +6187,7 @@
         <v>123</v>
       </c>
       <c r="C260" t="str">
-        <f>_xlfn.XLOOKUP(B260,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B260,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>INH</v>
       </c>
     </row>
@@ -6196,7 +6199,7 @@
         <v>123</v>
       </c>
       <c r="C261" t="str">
-        <f>_xlfn.XLOOKUP(B261,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B261,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>INH</v>
       </c>
     </row>
@@ -6208,7 +6211,7 @@
         <v>123</v>
       </c>
       <c r="C262" t="str">
-        <f>_xlfn.XLOOKUP(B262,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B262,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>INH</v>
       </c>
     </row>
@@ -6220,7 +6223,7 @@
         <v>128</v>
       </c>
       <c r="C263" t="str">
-        <f>_xlfn.XLOOKUP(B263,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B263,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>ISA</v>
       </c>
     </row>
@@ -6232,7 +6235,7 @@
         <v>132</v>
       </c>
       <c r="C264" t="str">
-        <f>_xlfn.XLOOKUP(B264,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B264,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>KAN</v>
       </c>
     </row>
@@ -6244,7 +6247,7 @@
         <v>247</v>
       </c>
       <c r="C265" t="str">
-        <f>_xlfn.XLOOKUP(B265,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B265,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CARBA</v>
       </c>
     </row>
@@ -6256,7 +6259,7 @@
         <v>567</v>
       </c>
       <c r="C266" t="str">
-        <f>_xlfn.XLOOKUP(B266,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B266,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>LOM</v>
       </c>
     </row>
@@ -6268,7 +6271,7 @@
         <v>147</v>
       </c>
       <c r="C267" t="str">
-        <f>_xlfn.XLOOKUP(B267,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B267,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>MEM_VAB</v>
       </c>
     </row>
@@ -6280,7 +6283,7 @@
         <v>569</v>
       </c>
       <c r="C268" t="str">
-        <f>_xlfn.XLOOKUP(B268,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B268,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>MEZ</v>
       </c>
     </row>
@@ -6292,7 +6295,7 @@
         <v>571</v>
       </c>
       <c r="C269" t="str">
-        <f>_xlfn.XLOOKUP(B269,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B269,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>MOX</v>
       </c>
     </row>
@@ -6304,7 +6307,7 @@
         <v>573</v>
       </c>
       <c r="C270" t="str">
-        <f>_xlfn.XLOOKUP(B270,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B270,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>MUP</v>
       </c>
     </row>
@@ -6316,7 +6319,7 @@
         <v>573</v>
       </c>
       <c r="C271" t="str">
-        <f>_xlfn.XLOOKUP(B271,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B271,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>MUP</v>
       </c>
     </row>
@@ -6328,7 +6331,7 @@
         <v>575</v>
       </c>
       <c r="C272" t="str">
-        <f>_xlfn.XLOOKUP(B272,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B272,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>NAF</v>
       </c>
     </row>
@@ -6340,7 +6343,7 @@
         <v>242</v>
       </c>
       <c r="C273" t="str">
-        <f>_xlfn.XLOOKUP(B273,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B273,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CARBA</v>
       </c>
     </row>
@@ -6352,7 +6355,7 @@
         <v>577</v>
       </c>
       <c r="C274" t="str">
-        <f>_xlfn.XLOOKUP(B274,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B274,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>NEO</v>
       </c>
     </row>
@@ -6364,7 +6367,7 @@
         <v>579</v>
       </c>
       <c r="C275" t="str">
-        <f>_xlfn.XLOOKUP(B275,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B275,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>NET</v>
       </c>
     </row>
@@ -6376,7 +6379,7 @@
         <v>166</v>
       </c>
       <c r="C276" t="str">
-        <f>_xlfn.XLOOKUP(B276,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B276,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>OFX</v>
       </c>
     </row>
@@ -6388,7 +6391,7 @@
         <v>239</v>
       </c>
       <c r="C277" t="str">
-        <f>_xlfn.XLOOKUP(B277,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B277,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CARBA</v>
       </c>
     </row>
@@ -6400,7 +6403,7 @@
         <v>170</v>
       </c>
       <c r="C278" t="str">
-        <f>_xlfn.XLOOKUP(B278,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B278,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>OXA</v>
       </c>
     </row>
@@ -6412,7 +6415,7 @@
         <v>170</v>
       </c>
       <c r="C279" t="str">
-        <f>_xlfn.XLOOKUP(B279,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B279,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>OXA</v>
       </c>
     </row>
@@ -6424,7 +6427,7 @@
         <v>581</v>
       </c>
       <c r="C280" t="str">
-        <f>_xlfn.XLOOKUP(B280,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B280,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>PAS</v>
       </c>
     </row>
@@ -6436,7 +6439,7 @@
         <v>581</v>
       </c>
       <c r="C281" t="str">
-        <f>_xlfn.XLOOKUP(B281,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B281,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>PAS</v>
       </c>
     </row>
@@ -6448,7 +6451,7 @@
         <v>172</v>
       </c>
       <c r="C282" t="str">
-        <f>_xlfn.XLOOKUP(B282,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B282,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>PEN</v>
       </c>
     </row>
@@ -6460,7 +6463,7 @@
         <v>172</v>
       </c>
       <c r="C283" t="str">
-        <f>_xlfn.XLOOKUP(B283,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B283,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>PEN</v>
       </c>
     </row>
@@ -6472,7 +6475,7 @@
         <v>220</v>
       </c>
       <c r="C284" t="str">
-        <f>_xlfn.XLOOKUP(B284,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B284,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>TZP</v>
       </c>
     </row>
@@ -6484,7 +6487,7 @@
         <v>183</v>
       </c>
       <c r="C285" t="str">
-        <f>_xlfn.XLOOKUP(B285,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B285,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>QUD</v>
       </c>
     </row>
@@ -6496,7 +6499,7 @@
         <v>187</v>
       </c>
       <c r="C286" t="str">
-        <f>_xlfn.XLOOKUP(B286,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B286,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>RIF</v>
       </c>
     </row>
@@ -6508,7 +6511,7 @@
         <v>94</v>
       </c>
       <c r="C287" t="str">
-        <f>_xlfn.XLOOKUP(B287,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B287,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>EMB_RIF</v>
       </c>
     </row>
@@ -6520,7 +6523,7 @@
         <v>187</v>
       </c>
       <c r="C288" t="str">
-        <f>_xlfn.XLOOKUP(B288,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B288,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>RIF</v>
       </c>
     </row>
@@ -6532,7 +6535,7 @@
         <v>187</v>
       </c>
       <c r="C289" t="str">
-        <f>_xlfn.XLOOKUP(B289,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B289,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>RIF</v>
       </c>
     </row>
@@ -6544,7 +6547,7 @@
         <v>583</v>
       </c>
       <c r="C290" t="str">
-        <f>_xlfn.XLOOKUP(B290,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B290,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>SPX</v>
       </c>
     </row>
@@ -6556,7 +6559,7 @@
         <v>193</v>
       </c>
       <c r="C291" t="str">
-        <f>_xlfn.XLOOKUP(B291,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B291,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>STR</v>
       </c>
     </row>
@@ -6568,7 +6571,7 @@
         <v>193</v>
       </c>
       <c r="C292" t="str">
-        <f>_xlfn.XLOOKUP(B292,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B292,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>STR</v>
       </c>
     </row>
@@ -6580,7 +6583,7 @@
         <v>193</v>
       </c>
       <c r="C293" t="str">
-        <f>_xlfn.XLOOKUP(B293,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B293,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>STR</v>
       </c>
     </row>
@@ -6592,7 +6595,7 @@
         <v>193</v>
       </c>
       <c r="C294" t="str">
-        <f>_xlfn.XLOOKUP(B294,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B294,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>STR</v>
       </c>
     </row>
@@ -6604,7 +6607,7 @@
         <v>193</v>
       </c>
       <c r="C295" t="str">
-        <f>_xlfn.XLOOKUP(B295,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B295,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>STR</v>
       </c>
     </row>
@@ -6616,7 +6619,7 @@
         <v>193</v>
       </c>
       <c r="C296" t="str">
-        <f>_xlfn.XLOOKUP(B296,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B296,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>STR</v>
       </c>
     </row>
@@ -6628,7 +6631,7 @@
         <v>193</v>
       </c>
       <c r="C297" t="str">
-        <f>_xlfn.XLOOKUP(B297,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B297,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>STR</v>
       </c>
     </row>
@@ -6640,7 +6643,7 @@
         <v>195</v>
       </c>
       <c r="C298" t="str">
-        <f>_xlfn.XLOOKUP(B298,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B298,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>SUL_DUR</v>
       </c>
     </row>
@@ -6652,7 +6655,7 @@
         <v>585</v>
       </c>
       <c r="C299" t="str">
-        <f>_xlfn.XLOOKUP(B299,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B299,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>SDI</v>
       </c>
     </row>
@@ -6664,7 +6667,7 @@
         <v>587</v>
       </c>
       <c r="C300" t="str">
-        <f>_xlfn.XLOOKUP(B300,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B300,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>SOX</v>
       </c>
     </row>
@@ -6676,7 +6679,7 @@
         <v>589</v>
       </c>
       <c r="C301" t="str">
-        <f>_xlfn.XLOOKUP(B301,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B301,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>TEC</v>
       </c>
     </row>
@@ -6688,7 +6691,7 @@
         <v>591</v>
       </c>
       <c r="C302" t="str">
-        <f>_xlfn.XLOOKUP(B302,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B302,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>THA</v>
       </c>
     </row>
@@ -6700,7 +6703,7 @@
         <v>206</v>
       </c>
       <c r="C303" t="str">
-        <f>_xlfn.XLOOKUP(B303,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B303,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>TIM</v>
       </c>
     </row>
@@ -6712,7 +6715,7 @@
         <v>204</v>
       </c>
       <c r="C304" t="str">
-        <f>_xlfn.XLOOKUP(B304,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B304,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>TIC</v>
       </c>
     </row>
@@ -6724,7 +6727,7 @@
         <v>199</v>
       </c>
       <c r="C305" t="str">
-        <f>_xlfn.XLOOKUP(B305,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B305,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>SXT</v>
       </c>
     </row>
@@ -6736,7 +6739,7 @@
         <v>199</v>
       </c>
       <c r="C306" t="str">
-        <f>_xlfn.XLOOKUP(B306,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B306,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>SXT</v>
       </c>
     </row>
@@ -6748,7 +6751,7 @@
         <v>593</v>
       </c>
       <c r="C307" t="str">
-        <f>_xlfn.XLOOKUP(B307,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B307,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>TVA</v>
       </c>
     </row>
@@ -6760,7 +6763,7 @@
         <v>246</v>
       </c>
       <c r="C308" t="str">
-        <f>_xlfn.XLOOKUP(B308,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B308,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CARBA</v>
       </c>
     </row>
@@ -6772,7 +6775,7 @@
         <v>581</v>
       </c>
       <c r="C309" t="str">
-        <f>_xlfn.XLOOKUP(B309,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B309,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>PAS</v>
       </c>
     </row>
@@ -6784,7 +6787,7 @@
         <v>19</v>
       </c>
       <c r="C310" t="str">
-        <f>_xlfn.XLOOKUP(B310,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B310,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>AMB</v>
       </c>
     </row>
@@ -6796,7 +6799,7 @@
         <v>19</v>
       </c>
       <c r="C311" t="str">
-        <f>_xlfn.XLOOKUP(B311,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B311,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>AMB</v>
       </c>
     </row>
@@ -6808,7 +6811,7 @@
         <v>19</v>
       </c>
       <c r="C312" t="str">
-        <f>_xlfn.XLOOKUP(B312,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B312,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>AMB</v>
       </c>
     </row>
@@ -6820,7 +6823,7 @@
         <v>656</v>
       </c>
       <c r="C313" t="str">
-        <f>_xlfn.XLOOKUP(B313,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B313,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>BAM</v>
       </c>
     </row>
@@ -6832,7 +6835,7 @@
         <v>550</v>
       </c>
       <c r="C314" t="str">
-        <f>_xlfn.XLOOKUP(B314,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B314,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CRB</v>
       </c>
     </row>
@@ -6844,7 +6847,7 @@
         <v>658</v>
       </c>
       <c r="C315" t="str">
-        <f>_xlfn.XLOOKUP(B315,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B315,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CFR</v>
       </c>
     </row>
@@ -6856,7 +6859,7 @@
         <v>660</v>
       </c>
       <c r="C316" t="str">
-        <f>_xlfn.XLOOKUP(B316,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B316,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CDR</v>
       </c>
     </row>
@@ -6868,7 +6871,7 @@
         <v>662</v>
       </c>
       <c r="C317" t="str">
-        <f>_xlfn.XLOOKUP(B317,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B317,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>DIT</v>
       </c>
     </row>
@@ -6880,7 +6883,7 @@
         <v>664</v>
       </c>
       <c r="C318" t="str">
-        <f>_xlfn.XLOOKUP(B318,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B318,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CMZ</v>
       </c>
     </row>
@@ -6892,7 +6895,7 @@
         <v>76</v>
       </c>
       <c r="C319" t="str">
-        <f>_xlfn.XLOOKUP(B319,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B319,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CTX</v>
       </c>
     </row>
@@ -6904,7 +6907,7 @@
         <v>76</v>
       </c>
       <c r="C320" t="str">
-        <f>_xlfn.XLOOKUP(B320,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B320,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CTX</v>
       </c>
     </row>
@@ -6916,7 +6919,7 @@
         <v>67</v>
       </c>
       <c r="C321" t="str">
-        <f>_xlfn.XLOOKUP(B321,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B321,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CPD</v>
       </c>
     </row>
@@ -6928,7 +6931,7 @@
         <v>666</v>
       </c>
       <c r="C322" t="str">
-        <f>_xlfn.XLOOKUP(B322,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B322,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CPR</v>
       </c>
     </row>
@@ -6940,7 +6943,7 @@
         <v>45</v>
       </c>
       <c r="C323" t="str">
-        <f>_xlfn.XLOOKUP(B323,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B323,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CAZ_AVI</v>
       </c>
     </row>
@@ -6952,7 +6955,7 @@
         <v>668</v>
       </c>
       <c r="C324" t="str">
-        <f>_xlfn.XLOOKUP(B324,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B324,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CTB</v>
       </c>
     </row>
@@ -6964,7 +6967,7 @@
         <v>71</v>
       </c>
       <c r="C325" t="str">
-        <f>_xlfn.XLOOKUP(B325,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B325,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CRO</v>
       </c>
     </row>
@@ -6976,7 +6979,7 @@
         <v>71</v>
       </c>
       <c r="C326" t="str">
-        <f>_xlfn.XLOOKUP(B326,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B326,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CRO</v>
       </c>
     </row>
@@ -6988,7 +6991,7 @@
         <v>80</v>
       </c>
       <c r="C327" t="str">
-        <f>_xlfn.XLOOKUP(B327,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B327,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CXM</v>
       </c>
     </row>
@@ -7000,7 +7003,7 @@
         <v>80</v>
       </c>
       <c r="C328" t="str">
-        <f>_xlfn.XLOOKUP(B328,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B328,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CXM</v>
       </c>
     </row>
@@ -7012,7 +7015,7 @@
         <v>670</v>
       </c>
       <c r="C329" t="str">
-        <f>_xlfn.XLOOKUP(B329,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B329,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>HAP</v>
       </c>
     </row>
@@ -7024,7 +7027,7 @@
         <v>672</v>
       </c>
       <c r="C330" t="str">
-        <f>_xlfn.XLOOKUP(B330,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B330,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CIN</v>
       </c>
     </row>
@@ -7036,7 +7039,7 @@
         <v>674</v>
       </c>
       <c r="C331" t="str">
-        <f>_xlfn.XLOOKUP(B331,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B331,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CLO</v>
       </c>
     </row>
@@ -7048,7 +7051,7 @@
         <v>9</v>
       </c>
       <c r="C332" t="str">
-        <f>_xlfn.XLOOKUP(B332,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B332,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CST</v>
       </c>
     </row>
@@ -7060,7 +7063,7 @@
         <v>9</v>
       </c>
       <c r="C333" t="str">
-        <f>_xlfn.XLOOKUP(B333,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B333,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CST</v>
       </c>
     </row>
@@ -7072,7 +7075,7 @@
         <v>243</v>
       </c>
       <c r="C334" t="str">
-        <f>_xlfn.XLOOKUP(B334,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B334,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>CARBA</v>
       </c>
     </row>
@@ -7084,7 +7087,7 @@
         <v>675</v>
       </c>
       <c r="C335" t="str">
-        <f>_xlfn.XLOOKUP(B335,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B335,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>DEM</v>
       </c>
     </row>
@@ -7096,7 +7099,7 @@
         <v>677</v>
       </c>
       <c r="C336" t="str">
-        <f>_xlfn.XLOOKUP(B336,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B336,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>DIR</v>
       </c>
     </row>
@@ -7108,7 +7111,7 @@
         <v>679</v>
       </c>
       <c r="C337" t="str">
-        <f>_xlfn.XLOOKUP(B337,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B337,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>ENX</v>
       </c>
     </row>
@@ -7120,7 +7123,7 @@
         <v>681</v>
       </c>
       <c r="C338" t="str">
-        <f>_xlfn.XLOOKUP(B338,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B338,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>GEM</v>
       </c>
     </row>
@@ -7132,7 +7135,7 @@
         <v>5</v>
       </c>
       <c r="C339" t="str">
-        <f>_xlfn.XLOOKUP(B339,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B339,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>GEN</v>
       </c>
     </row>
@@ -7144,7 +7147,7 @@
         <v>683</v>
       </c>
       <c r="C340" t="str">
-        <f>_xlfn.XLOOKUP(B340,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B340,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>GRX</v>
       </c>
     </row>
@@ -7156,7 +7159,7 @@
         <v>126</v>
       </c>
       <c r="C341" t="str">
-        <f>_xlfn.XLOOKUP(B341,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B341,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>IPM_REL</v>
       </c>
     </row>
@@ -7168,7 +7171,7 @@
         <v>7</v>
       </c>
       <c r="C342" t="str">
-        <f>_xlfn.XLOOKUP(B342,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B342,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>IPM</v>
       </c>
     </row>
@@ -7180,7 +7183,7 @@
         <v>685</v>
       </c>
       <c r="C343" t="str">
-        <f>_xlfn.XLOOKUP(B343,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B343,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>LMU</v>
       </c>
     </row>
@@ -7192,7 +7195,7 @@
         <v>687</v>
       </c>
       <c r="C344" t="str">
-        <f>_xlfn.XLOOKUP(B344,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B344,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>LIN</v>
       </c>
     </row>
@@ -7204,7 +7207,7 @@
         <v>689</v>
       </c>
       <c r="C345" t="str">
-        <f>_xlfn.XLOOKUP(B345,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B345,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>LOR</v>
       </c>
     </row>
@@ -7216,7 +7219,7 @@
         <v>147</v>
       </c>
       <c r="C346" t="str">
-        <f>_xlfn.XLOOKUP(B346,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B346,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>MEM_VAB</v>
       </c>
     </row>
@@ -7228,7 +7231,7 @@
         <v>691</v>
       </c>
       <c r="C347" t="str">
-        <f>_xlfn.XLOOKUP(B347,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B347,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>NTZ</v>
       </c>
     </row>
@@ -7240,7 +7243,7 @@
         <v>693</v>
       </c>
       <c r="C348" t="str">
-        <f>_xlfn.XLOOKUP(B348,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B348,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>NIZ</v>
       </c>
     </row>
@@ -7252,7 +7255,7 @@
         <v>162</v>
       </c>
       <c r="C349" t="str">
-        <f>_xlfn.XLOOKUP(B349,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B349,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>NOR</v>
       </c>
     </row>
@@ -7264,7 +7267,7 @@
         <v>695</v>
       </c>
       <c r="C350" t="str">
-        <f>_xlfn.XLOOKUP(B350,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B350,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>NOV</v>
       </c>
     </row>
@@ -7276,7 +7279,7 @@
         <v>697</v>
       </c>
       <c r="C351" t="str">
-        <f>_xlfn.XLOOKUP(B351,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B351,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>ORI</v>
       </c>
     </row>
@@ -7288,7 +7291,7 @@
         <v>699</v>
       </c>
       <c r="C352" t="str">
-        <f>_xlfn.XLOOKUP(B352,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B352,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>PAR</v>
       </c>
     </row>
@@ -7300,7 +7303,7 @@
         <v>172</v>
       </c>
       <c r="C353" t="str">
-        <f>_xlfn.XLOOKUP(B353,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B353,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>PEN</v>
       </c>
     </row>
@@ -7312,7 +7315,7 @@
         <v>172</v>
       </c>
       <c r="C354" t="str">
-        <f>_xlfn.XLOOKUP(B354,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B354,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>PEN</v>
       </c>
     </row>
@@ -7324,7 +7327,7 @@
         <v>172</v>
       </c>
       <c r="C355" t="str">
-        <f>_xlfn.XLOOKUP(B355,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B355,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>PEN</v>
       </c>
     </row>
@@ -7336,7 +7339,7 @@
         <v>172</v>
       </c>
       <c r="C356" t="str">
-        <f>_xlfn.XLOOKUP(B356,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B356,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>PEN</v>
       </c>
     </row>
@@ -7348,7 +7351,7 @@
         <v>220</v>
       </c>
       <c r="C357" t="str">
-        <f>_xlfn.XLOOKUP(B357,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B357,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>TZP</v>
       </c>
     </row>
@@ -7360,7 +7363,7 @@
         <v>183</v>
       </c>
       <c r="C358" t="str">
-        <f>_xlfn.XLOOKUP(B358,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B358,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>QUD</v>
       </c>
     </row>
@@ -7372,7 +7375,7 @@
         <v>701</v>
       </c>
       <c r="C359" t="str">
-        <f>_xlfn.XLOOKUP(B359,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B359,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>RET</v>
       </c>
     </row>
@@ -7384,7 +7387,7 @@
         <v>704</v>
       </c>
       <c r="C360" t="str">
-        <f>_xlfn.XLOOKUP(B360,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B360,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>RPT</v>
       </c>
     </row>
@@ -7396,7 +7399,7 @@
         <v>705</v>
       </c>
       <c r="C361" t="str">
-        <f>_xlfn.XLOOKUP(B361,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B361,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>RFX</v>
       </c>
     </row>
@@ -7408,7 +7411,7 @@
         <v>707</v>
       </c>
       <c r="C362" t="str">
-        <f>_xlfn.XLOOKUP(B362,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B362,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>SPI</v>
       </c>
     </row>
@@ -7420,7 +7423,7 @@
         <v>709</v>
       </c>
       <c r="C363" t="str">
-        <f>_xlfn.XLOOKUP(B363,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B363,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>TZD</v>
       </c>
     </row>
@@ -7432,7 +7435,7 @@
         <v>711</v>
       </c>
       <c r="C364" t="str">
-        <f>_xlfn.XLOOKUP(B364,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B364,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>TLT</v>
       </c>
     </row>
@@ -7444,7 +7447,7 @@
         <v>206</v>
       </c>
       <c r="C365" t="str">
-        <f>_xlfn.XLOOKUP(B365,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B365,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>TIM</v>
       </c>
     </row>
@@ -7456,7 +7459,7 @@
         <v>206</v>
       </c>
       <c r="C366" t="str">
-        <f>_xlfn.XLOOKUP(B366,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$B$2:$B$10055)</f>
+        <f>_xlfn.XLOOKUP(B366,antibiotic_code_map!$A$2:$A$10055,antibiotic_code_map!$C$2:$C$10055)</f>
         <v>TIM</v>
       </c>
     </row>
@@ -7479,1489 +7482,2020 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9CF1F8C-C758-0C4E-B057-A5D75AA8605E}">
-  <dimension ref="A1:D177"/>
+  <dimension ref="A1:E177"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="38.5" customWidth="1"/>
-    <col min="2" max="2" width="19.83203125" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="3" max="3" width="19.83203125" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>23</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>27</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>21</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>189</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>17</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>33</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>546</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>29</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>31</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>656</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>548</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>35</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>224</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16" t="s">
         <v>36</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>224</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>38</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>241</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
         <v>39</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>225</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>247</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
         <v>39</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>225</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>242</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20" t="s">
         <v>39</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>225</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>243</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
         <v>39</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>239</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
         <v>39</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>225</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>246</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23" t="s">
         <v>39</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>225</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>550</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>41</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>49</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>658</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27" t="s">
         <v>659</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>106</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>55</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>660</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30" t="s">
         <v>661</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>662</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>110</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>108</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>53</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>664</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35">
+        <v>1</v>
+      </c>
+      <c r="C35" t="s">
         <v>665</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>552</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36">
+        <v>1</v>
+      </c>
+      <c r="C36" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>554</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>597</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>76</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="C39" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>78</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="C40" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>74</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41">
+        <v>1</v>
+      </c>
+      <c r="C41" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>556</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="C42" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>115</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>67</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>666</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="C45" t="s">
         <v>667</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>69</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46">
+        <v>1</v>
+      </c>
+      <c r="C46" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>43</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>45</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48">
+        <v>1</v>
+      </c>
+      <c r="C48" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>47</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49">
+        <v>1</v>
+      </c>
+      <c r="C49" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>668</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>249</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51">
+        <v>1</v>
+      </c>
+      <c r="C51" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>214</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52">
+        <v>1</v>
+      </c>
+      <c r="C52" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>71</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53">
+        <v>1</v>
+      </c>
+      <c r="C53" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>80</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54">
+        <v>1</v>
+      </c>
+      <c r="C54" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>558</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55">
+        <v>1</v>
+      </c>
+      <c r="C55" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>51</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56">
+        <v>1</v>
+      </c>
+      <c r="C56" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>670</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57">
+        <v>1</v>
+      </c>
+      <c r="C57" t="s">
         <v>671</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>560</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58">
+        <v>1</v>
+      </c>
+      <c r="C58" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>57</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59">
+        <v>1</v>
+      </c>
+      <c r="C59" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>672</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60">
+        <v>1</v>
+      </c>
+      <c r="C60" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>1</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61">
+        <v>1</v>
+      </c>
+      <c r="C61" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>63</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="C62" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>562</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63">
+        <v>1</v>
+      </c>
+      <c r="C63" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>4</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64">
+        <v>1</v>
+      </c>
+      <c r="C64" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>61</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65">
+        <v>1</v>
+      </c>
+      <c r="C65" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>65</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66">
+        <v>1</v>
+      </c>
+      <c r="C66" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>674</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67">
+        <v>1</v>
+      </c>
+      <c r="C67" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>9</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68">
+        <v>1</v>
+      </c>
+      <c r="C68" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>84</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69">
+        <v>1</v>
+      </c>
+      <c r="C69" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>545</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70">
+        <v>1</v>
+      </c>
+      <c r="C70" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>82</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71">
+        <v>1</v>
+      </c>
+      <c r="C71" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>86</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72">
+        <v>1</v>
+      </c>
+      <c r="C72" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>675</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73">
+        <v>1</v>
+      </c>
+      <c r="C73" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>565</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74">
+        <v>1</v>
+      </c>
+      <c r="C74" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>677</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75">
+        <v>1</v>
+      </c>
+      <c r="C75" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>88</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76">
+        <v>1</v>
+      </c>
+      <c r="C76" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>90</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77">
+        <v>1</v>
+      </c>
+      <c r="C77" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>679</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78">
+        <v>1</v>
+      </c>
+      <c r="C78" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>96</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79">
+        <v>1</v>
+      </c>
+      <c r="C79" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>103</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80">
+        <v>1</v>
+      </c>
+      <c r="C80" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>98</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81">
+        <v>1</v>
+      </c>
+      <c r="C81" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>92</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82">
+        <v>1</v>
+      </c>
+      <c r="C82" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>94</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83">
+        <v>1</v>
+      </c>
+      <c r="C83" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>101</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84">
+        <v>1</v>
+      </c>
+      <c r="C84" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>244</v>
       </c>
-      <c r="B85" t="s">
-        <v>99</v>
+      <c r="B85">
+        <v>1</v>
       </c>
       <c r="C85" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D85" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>112</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86">
+        <v>1</v>
+      </c>
+      <c r="C86" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>15</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87">
+        <v>1</v>
+      </c>
+      <c r="C87" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>0</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88">
+        <v>1</v>
+      </c>
+      <c r="C88" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>251</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89">
+        <v>1</v>
+      </c>
+      <c r="C89" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>117</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90">
+        <v>1</v>
+      </c>
+      <c r="C90" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>681</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91">
+        <v>1</v>
+      </c>
+      <c r="C91" t="s">
         <v>682</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>5</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92">
+        <v>1</v>
+      </c>
+      <c r="C92" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>683</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93">
+        <v>1</v>
+      </c>
+      <c r="C93" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>120</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94">
+        <v>1</v>
+      </c>
+      <c r="C94" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>7</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95">
+        <v>1</v>
+      </c>
+      <c r="C95" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>126</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96">
+        <v>1</v>
+      </c>
+      <c r="C96" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>236</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97">
+        <v>1</v>
+      </c>
+      <c r="C97" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>128</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98">
+        <v>1</v>
+      </c>
+      <c r="C98" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>123</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99">
+        <v>1</v>
+      </c>
+      <c r="C99" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>130</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100">
+        <v>1</v>
+      </c>
+      <c r="C100" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>132</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101">
+        <v>1</v>
+      </c>
+      <c r="C101" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>134</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102">
+        <v>1</v>
+      </c>
+      <c r="C102" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>685</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103">
+        <v>1</v>
+      </c>
+      <c r="C103" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>2</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104">
+        <v>1</v>
+      </c>
+      <c r="C104" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>687</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105">
+        <v>1</v>
+      </c>
+      <c r="C105" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>137</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106">
+        <v>1</v>
+      </c>
+      <c r="C106" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>567</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107">
+        <v>1</v>
+      </c>
+      <c r="C107" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>689</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108">
+        <v>1</v>
+      </c>
+      <c r="C108" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>143</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109">
+        <v>1</v>
+      </c>
+      <c r="C109" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>145</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110">
+        <v>1</v>
+      </c>
+      <c r="C110" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>147</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111">
+        <v>1</v>
+      </c>
+      <c r="C111" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>153</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112">
+        <v>1</v>
+      </c>
+      <c r="C112" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>569</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113">
+        <v>1</v>
+      </c>
+      <c r="C113" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>149</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114">
+        <v>1</v>
+      </c>
+      <c r="C114" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>140</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115">
+        <v>1</v>
+      </c>
+      <c r="C115" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>151</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B116">
+        <v>1</v>
+      </c>
+      <c r="C116" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>240</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117">
+        <v>1</v>
+      </c>
+      <c r="C117" t="s">
         <v>138</v>
       </c>
-      <c r="C117" t="s">
+      <c r="D117" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>571</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118">
+        <v>1</v>
+      </c>
+      <c r="C118" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>155</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119">
+        <v>1</v>
+      </c>
+      <c r="C119" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>573</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120">
+        <v>1</v>
+      </c>
+      <c r="C120" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>575</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B121">
+        <v>1</v>
+      </c>
+      <c r="C121" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>250</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122">
+        <v>1</v>
+      </c>
+      <c r="C122" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>158</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123">
+        <v>1</v>
+      </c>
+      <c r="C123" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>577</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124">
+        <v>1</v>
+      </c>
+      <c r="C124" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>579</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125">
+        <v>1</v>
+      </c>
+      <c r="C125" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>691</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126">
+        <v>1</v>
+      </c>
+      <c r="C126" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>160</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127">
+        <v>1</v>
+      </c>
+      <c r="C127" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>693</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128">
+        <v>1</v>
+      </c>
+      <c r="C128" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>162</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129">
+        <v>1</v>
+      </c>
+      <c r="C129" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>695</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B130">
+        <v>1</v>
+      </c>
+      <c r="C130" t="s">
         <v>696</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>164</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131">
+        <v>1</v>
+      </c>
+      <c r="C131" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>166</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132">
+        <v>1</v>
+      </c>
+      <c r="C132" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>168</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133">
+        <v>1</v>
+      </c>
+      <c r="C133" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>697</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134">
+        <v>1</v>
+      </c>
+      <c r="C134" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>170</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135">
+        <v>1</v>
+      </c>
+      <c r="C135" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>581</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136">
+        <v>1</v>
+      </c>
+      <c r="C136" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>699</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137">
+        <v>1</v>
+      </c>
+      <c r="C137" t="s">
         <v>700</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>172</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138">
+        <v>1</v>
+      </c>
+      <c r="C138" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>245</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B139">
+        <v>1</v>
+      </c>
+      <c r="C139" t="s">
         <v>141</v>
       </c>
-      <c r="C139" t="s">
+      <c r="D139" t="s">
         <v>226</v>
       </c>
-      <c r="D139" t="s">
+      <c r="E139" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>8</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B140">
+        <v>1</v>
+      </c>
+      <c r="C140" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>220</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B141">
+        <v>1</v>
+      </c>
+      <c r="C141" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>175</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B142">
+        <v>1</v>
+      </c>
+      <c r="C142" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>177</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B143">
+        <v>1</v>
+      </c>
+      <c r="C143" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>179</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B144">
+        <v>1</v>
+      </c>
+      <c r="C144" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>181</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B145">
+        <v>1</v>
+      </c>
+      <c r="C145" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>183</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B146">
+        <v>1</v>
+      </c>
+      <c r="C146" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>701</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B147">
+        <v>1</v>
+      </c>
+      <c r="C147" t="s">
         <v>702</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>248</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B148">
+        <v>1</v>
+      </c>
+      <c r="C148" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>185</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B149">
+        <v>1</v>
+      </c>
+      <c r="C149" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>187</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B150">
+        <v>1</v>
+      </c>
+      <c r="C150" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>704</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B151">
+        <v>1</v>
+      </c>
+      <c r="C151" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>705</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B152">
+        <v>1</v>
+      </c>
+      <c r="C152" t="s">
         <v>706</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>583</v>
       </c>
-      <c r="B153" t="s">
+      <c r="B153">
+        <v>1</v>
+      </c>
+      <c r="C153" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>191</v>
       </c>
-      <c r="B154" t="s">
+      <c r="B154">
+        <v>1</v>
+      </c>
+      <c r="C154" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>707</v>
       </c>
-      <c r="B155" t="s">
+      <c r="B155">
+        <v>1</v>
+      </c>
+      <c r="C155" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>193</v>
       </c>
-      <c r="B156" t="s">
+      <c r="B156">
+        <v>1</v>
+      </c>
+      <c r="C156" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>195</v>
       </c>
-      <c r="B157" t="s">
+      <c r="B157">
+        <v>1</v>
+      </c>
+      <c r="C157" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>585</v>
       </c>
-      <c r="B158" t="s">
+      <c r="B158">
+        <v>1</v>
+      </c>
+      <c r="C158" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>197</v>
       </c>
-      <c r="B159" t="s">
+      <c r="B159">
+        <v>1</v>
+      </c>
+      <c r="C159" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>587</v>
       </c>
-      <c r="B160" t="s">
+      <c r="B160">
+        <v>1</v>
+      </c>
+      <c r="C160" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>709</v>
       </c>
-      <c r="B161" t="s">
+      <c r="B161">
+        <v>1</v>
+      </c>
+      <c r="C161" t="s">
         <v>710</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>589</v>
       </c>
-      <c r="B162" t="s">
+      <c r="B162">
+        <v>1</v>
+      </c>
+      <c r="C162" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>208</v>
       </c>
-      <c r="B163" t="s">
+      <c r="B163">
+        <v>1</v>
+      </c>
+      <c r="C163" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>711</v>
       </c>
-      <c r="B164" t="s">
+      <c r="B164">
+        <v>1</v>
+      </c>
+      <c r="C164" t="s">
         <v>712</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>216</v>
       </c>
-      <c r="B165" t="s">
+      <c r="B165">
+        <v>1</v>
+      </c>
+      <c r="C165" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>218</v>
       </c>
-      <c r="B166" t="s">
+      <c r="B166">
+        <v>1</v>
+      </c>
+      <c r="C166" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>201</v>
       </c>
-      <c r="B167" t="s">
+      <c r="B167">
+        <v>1</v>
+      </c>
+      <c r="C167" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>591</v>
       </c>
-      <c r="B168" t="s">
+      <c r="B168">
+        <v>1</v>
+      </c>
+      <c r="C168" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>204</v>
       </c>
-      <c r="B169" t="s">
+      <c r="B169">
+        <v>1</v>
+      </c>
+      <c r="C169" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>206</v>
       </c>
-      <c r="B170" t="s">
+      <c r="B170">
+        <v>1</v>
+      </c>
+      <c r="C170" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>6</v>
       </c>
-      <c r="B171" t="s">
+      <c r="B171">
+        <v>1</v>
+      </c>
+      <c r="C171" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>212</v>
       </c>
-      <c r="B172" t="s">
+      <c r="B172">
+        <v>1</v>
+      </c>
+      <c r="C172" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>210</v>
       </c>
-      <c r="B173" t="s">
+      <c r="B173">
+        <v>1</v>
+      </c>
+      <c r="C173" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>199</v>
       </c>
-      <c r="B174" t="s">
+      <c r="B174">
+        <v>1</v>
+      </c>
+      <c r="C174" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>593</v>
       </c>
-      <c r="B175" t="s">
+      <c r="B175">
+        <v>1</v>
+      </c>
+      <c r="C175" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>3</v>
       </c>
-      <c r="B176" t="s">
+      <c r="B176">
+        <v>1</v>
+      </c>
+      <c r="C176" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>12</v>
       </c>
-      <c r="B177" t="s">
+      <c r="B177">
+        <v>1</v>
+      </c>
+      <c r="C177" t="s">
         <v>222</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D177">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E177">
     <sortCondition ref="A2:A177"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
